--- a/Data/accc_petrol_prices_q1_2025.xlsx
+++ b/Data/accc_petrol_prices_q1_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2086D22E-1017-4DBE-ACEC-B267A8A700D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{2086D22E-1017-4DBE-ACEC-B267A8A700D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A7352E0-A879-419E-9873-05F667EE8F4F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{22D3EFBE-B125-4FA6-A5EC-E51B41E18094}"/>
+    <workbookView minimized="1" xWindow="2895" yWindow="3180" windowWidth="21600" windowHeight="11265" xr2:uid="{22D3EFBE-B125-4FA6-A5EC-E51B41E18094}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,10 +99,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -124,13 +131,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -542,7 +552,7 @@
       <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -613,7 +623,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{36DB8F3A-8A7B-4C5B-88FB-8DE8C35266E9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>